--- a/Updated 2026 Easter Projections.xlsx
+++ b/Updated 2026 Easter Projections.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron.Mobley\Desktop\Campus_Projections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AA11FD-C8D3-4BDF-96CF-9C72ACD61C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733C44AD-E801-4659-9D6D-769259954245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58CE65A0-2C74-47D2-A21E-7237ADCF0C72}"/>
   </bookViews>
@@ -47,12 +47,6 @@
     <t>Day</t>
   </si>
   <si>
-    <t>ServiceDateTime</t>
-  </si>
-  <si>
-    <t>AdultCapacity</t>
-  </si>
-  <si>
     <t>Arlington</t>
   </si>
   <si>
@@ -105,6 +99,12 @@
   </si>
   <si>
     <t>Service Attendance</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Adult Capacity</t>
   </si>
 </sst>
 </file>
@@ -160,14 +160,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -178,22 +171,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{168BCDE0-C5DA-4658-8EB1-A3B94C648440}" name="Table1" displayName="Table1" ref="A1:G64" totalsRowShown="0">
-  <autoFilter ref="A1:G64" xr:uid="{168BCDE0-C5DA-4658-8EB1-A3B94C648440}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EBF46011-FEAA-4385-8D90-3EB5EC08BFF6}" name="SundayDate" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{E5D8D5DD-1487-4BD2-AAB0-38B74D467EAD}" name="Campus"/>
-    <tableColumn id="4" xr3:uid="{4A729DB0-D509-4E18-B04E-E2E1B38B756C}" name="Day"/>
-    <tableColumn id="5" xr3:uid="{DF85AF0A-7279-47E5-84EB-7298EAC2DC09}" name="ServiceDateTime" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{09BAE611-8122-4A88-81DF-E284102C9E27}" name="Service Attendance"/>
-    <tableColumn id="8" xr3:uid="{66B861CD-85CA-416D-8A4B-6DB420363361}" name="AdultCapacity"/>
-    <tableColumn id="9" xr3:uid="{ABD328B6-DB81-4D28-9A7A-22609A9CDEA1}" name="Total Attendance"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -516,7 +493,7 @@
   <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" style="2" customWidth="1"/>
@@ -535,17 +512,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
+      <c r="D1" t="s">
+        <v>21</v>
       </c>
       <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -553,12 +530,12 @@
         <v>46117</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>0.72361111111111109</v>
       </c>
       <c r="E2">
@@ -576,12 +553,12 @@
         <v>46117</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>0.80694444444444446</v>
       </c>
       <c r="E3">
@@ -599,12 +576,12 @@
         <v>46117</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4">
         <v>0.39027777777777778</v>
       </c>
       <c r="E4">
@@ -622,12 +599,12 @@
         <v>46117</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5">
         <v>0.47361111111111109</v>
       </c>
       <c r="E5">
@@ -645,12 +622,12 @@
         <v>46117</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6">
         <v>0.72361111111111109</v>
       </c>
       <c r="E6">
@@ -668,12 +645,12 @@
         <v>46117</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7">
         <v>0.80694444444444446</v>
       </c>
       <c r="E7">
@@ -691,12 +668,12 @@
         <v>46117</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8">
         <v>0.39027777777777778</v>
       </c>
       <c r="E8">
@@ -714,12 +691,12 @@
         <v>46117</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9">
         <v>0.47361111111111109</v>
       </c>
       <c r="E9">
@@ -737,12 +714,12 @@
         <v>46117</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="D10">
         <v>0.72361111111111109</v>
       </c>
       <c r="E10">
@@ -760,12 +737,12 @@
         <v>46117</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11">
         <v>0.80694444444444446</v>
       </c>
       <c r="E11">
@@ -783,12 +760,12 @@
         <v>46117</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2">
+        <v>8</v>
+      </c>
+      <c r="D12">
         <v>0.64027777777777772</v>
       </c>
       <c r="E12">
@@ -806,12 +783,12 @@
         <v>46117</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13">
         <v>0.72361111111111109</v>
       </c>
       <c r="E13">
@@ -829,12 +806,12 @@
         <v>46117</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="D14">
         <v>0.30694444444444446</v>
       </c>
       <c r="E14">
@@ -852,12 +829,12 @@
         <v>46117</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2">
+        <v>5</v>
+      </c>
+      <c r="D15">
         <v>0.39027777777777778</v>
       </c>
       <c r="E15">
@@ -875,12 +852,12 @@
         <v>46117</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16">
         <v>0.47361111111111109</v>
       </c>
       <c r="E16">
@@ -898,12 +875,12 @@
         <v>46117</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2">
+        <v>5</v>
+      </c>
+      <c r="D17">
         <v>0.68194444444444446</v>
       </c>
       <c r="E17">
@@ -921,12 +898,12 @@
         <v>46117</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2">
+        <v>4</v>
+      </c>
+      <c r="D18">
         <v>0.80694444444444446</v>
       </c>
       <c r="E18">
@@ -944,12 +921,12 @@
         <v>46117</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2">
+        <v>8</v>
+      </c>
+      <c r="D19">
         <v>0.72361111111111109</v>
       </c>
       <c r="E19">
@@ -967,12 +944,12 @@
         <v>46117</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="2">
+        <v>5</v>
+      </c>
+      <c r="D20">
         <v>0.39027777777777778</v>
       </c>
       <c r="E20">
@@ -990,12 +967,12 @@
         <v>46117</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="2">
+        <v>5</v>
+      </c>
+      <c r="D21">
         <v>0.47361111111111109</v>
       </c>
       <c r="E21">
@@ -1013,12 +990,12 @@
         <v>46117</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="D22">
         <v>0.80694444444444446</v>
       </c>
       <c r="E22">
@@ -1036,12 +1013,12 @@
         <v>46117</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23">
         <v>0.39027777777777778</v>
       </c>
       <c r="E23">
@@ -1059,12 +1036,12 @@
         <v>46117</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="D24">
         <v>0.47361111111111109</v>
       </c>
       <c r="E24">
@@ -1082,12 +1059,12 @@
         <v>46117</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25">
         <v>0.80694444444444446</v>
       </c>
       <c r="E25">
@@ -1105,12 +1082,12 @@
         <v>46117</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2">
+        <v>8</v>
+      </c>
+      <c r="D26">
         <v>0.72361111111111109</v>
       </c>
       <c r="E26">
@@ -1128,12 +1105,12 @@
         <v>46117</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27">
         <v>0.30694444444444446</v>
       </c>
       <c r="E27">
@@ -1151,12 +1128,12 @@
         <v>46117</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28">
         <v>0.39027777777777778</v>
       </c>
       <c r="E28">
@@ -1174,12 +1151,12 @@
         <v>46117</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="2">
+        <v>5</v>
+      </c>
+      <c r="D29">
         <v>0.47361111111111109</v>
       </c>
       <c r="E29">
@@ -1197,12 +1174,12 @@
         <v>46117</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30">
         <v>0.72361111111111109</v>
       </c>
       <c r="E30">
@@ -1220,12 +1197,12 @@
         <v>46117</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2">
+        <v>4</v>
+      </c>
+      <c r="D31">
         <v>0.80694444444444446</v>
       </c>
       <c r="E31">
@@ -1243,12 +1220,12 @@
         <v>46117</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32">
         <v>0.39027777777777778</v>
       </c>
       <c r="E32">
@@ -1266,12 +1243,12 @@
         <v>46117</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="D33">
         <v>0.47361111111111109</v>
       </c>
       <c r="E33">
@@ -1289,12 +1266,12 @@
         <v>46117</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="2">
+        <v>4</v>
+      </c>
+      <c r="D34">
         <v>0.80694444444444446</v>
       </c>
       <c r="E34">
@@ -1312,12 +1289,12 @@
         <v>46117</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="2">
+        <v>5</v>
+      </c>
+      <c r="D35">
         <v>0.39027777777777778</v>
       </c>
       <c r="E35">
@@ -1335,12 +1312,12 @@
         <v>46117</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="2">
+        <v>5</v>
+      </c>
+      <c r="D36">
         <v>0.47361111111111109</v>
       </c>
       <c r="E36">
@@ -1358,12 +1335,12 @@
         <v>46117</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2">
+        <v>8</v>
+      </c>
+      <c r="D37">
         <v>0.64027777777777772</v>
       </c>
       <c r="E37">
@@ -1381,12 +1358,12 @@
         <v>46117</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="2">
+        <v>5</v>
+      </c>
+      <c r="D38">
         <v>0.30694444444444446</v>
       </c>
       <c r="E38">
@@ -1404,12 +1381,12 @@
         <v>46117</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="2">
+        <v>5</v>
+      </c>
+      <c r="D39">
         <v>0.39027777777777778</v>
       </c>
       <c r="E39">
@@ -1427,12 +1404,12 @@
         <v>46117</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="2">
+        <v>5</v>
+      </c>
+      <c r="D40">
         <v>0.47361111111111109</v>
       </c>
       <c r="E40">
@@ -1450,12 +1427,12 @@
         <v>46117</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="D41">
         <v>0.72361111111111109</v>
       </c>
       <c r="E41">
@@ -1473,12 +1450,12 @@
         <v>46117</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="D42">
         <v>0.80694444444444446</v>
       </c>
       <c r="E42">
@@ -1496,12 +1473,12 @@
         <v>46117</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2">
+        <v>8</v>
+      </c>
+      <c r="D43">
         <v>0.64027777777777772</v>
       </c>
       <c r="E43">
@@ -1519,12 +1496,12 @@
         <v>46117</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2">
+        <v>8</v>
+      </c>
+      <c r="D44">
         <v>0.72361111111111109</v>
       </c>
       <c r="E44">
@@ -1542,12 +1519,12 @@
         <v>46117</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="2">
+        <v>5</v>
+      </c>
+      <c r="D45">
         <v>0.30694444444444446</v>
       </c>
       <c r="E45">
@@ -1565,12 +1542,12 @@
         <v>46117</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="2">
+        <v>5</v>
+      </c>
+      <c r="D46">
         <v>0.39027777777777778</v>
       </c>
       <c r="E46">
@@ -1588,12 +1565,12 @@
         <v>46117</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="2">
+        <v>5</v>
+      </c>
+      <c r="D47">
         <v>0.47361111111111109</v>
       </c>
       <c r="E47">
@@ -1611,12 +1588,12 @@
         <v>46117</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="D48">
         <v>0.18194444444444444</v>
       </c>
       <c r="E48">
@@ -1634,12 +1611,12 @@
         <v>46117</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="2">
+        <v>4</v>
+      </c>
+      <c r="D49">
         <v>0.72361111111111109</v>
       </c>
       <c r="E49">
@@ -1657,12 +1634,12 @@
         <v>46117</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50">
         <v>0.80694444444444446</v>
       </c>
       <c r="E50">
@@ -1680,12 +1657,12 @@
         <v>46117</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51">
         <v>0.39027777777777778</v>
       </c>
       <c r="E51">
@@ -1703,12 +1680,12 @@
         <v>46117</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="D52">
         <v>0.47361111111111109</v>
       </c>
       <c r="E52">
@@ -1726,12 +1703,12 @@
         <v>46117</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2">
+        <v>4</v>
+      </c>
+      <c r="D53">
         <v>0.72361111111111109</v>
       </c>
       <c r="E53">
@@ -1749,12 +1726,12 @@
         <v>46117</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="2">
+        <v>4</v>
+      </c>
+      <c r="D54">
         <v>0.80694444444444446</v>
       </c>
       <c r="E54">
@@ -1772,12 +1749,12 @@
         <v>46117</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2">
+        <v>8</v>
+      </c>
+      <c r="D55">
         <v>0.64027777777777772</v>
       </c>
       <c r="E55">
@@ -1795,12 +1772,12 @@
         <v>46117</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2">
+        <v>8</v>
+      </c>
+      <c r="D56">
         <v>0.72361111111111109</v>
       </c>
       <c r="E56">
@@ -1818,12 +1795,12 @@
         <v>46117</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="2">
+        <v>5</v>
+      </c>
+      <c r="D57">
         <v>0.30694444444444446</v>
       </c>
       <c r="E57">
@@ -1841,12 +1818,12 @@
         <v>46117</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58">
         <v>0.39027777777777778</v>
       </c>
       <c r="E58">
@@ -1864,12 +1841,12 @@
         <v>46117</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59">
         <v>0.47361111111111109</v>
       </c>
       <c r="E59">
@@ -1887,12 +1864,12 @@
         <v>46117</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60">
         <v>0.68194444444444446</v>
       </c>
       <c r="E60">
@@ -1910,12 +1887,12 @@
         <v>46117</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2">
+        <v>8</v>
+      </c>
+      <c r="D61">
         <v>0.64027777777777772</v>
       </c>
       <c r="E61">
@@ -1933,12 +1910,12 @@
         <v>46117</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="2">
+        <v>5</v>
+      </c>
+      <c r="D62">
         <v>0.30694444444444446</v>
       </c>
       <c r="E62">
@@ -1956,12 +1933,12 @@
         <v>46117</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="2">
+        <v>5</v>
+      </c>
+      <c r="D63">
         <v>0.39027777777777778</v>
       </c>
       <c r="E63">
@@ -1979,12 +1956,12 @@
         <v>46117</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="2">
+        <v>5</v>
+      </c>
+      <c r="D64">
         <v>0.47361111111111109</v>
       </c>
       <c r="E64">
@@ -2002,8 +1979,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>